--- a/Tabla de endpoints.xlsx
+++ b/Tabla de endpoints.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142CE8E5-09B3-4B9E-BC31-7A199614921F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F34AEC-94F5-4962-9A7F-7500F34C6D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitácora" sheetId="1" r:id="rId1"/>
-    <sheet name="Admin" sheetId="2" r:id="rId2"/>
-    <sheet name="Clientes" sheetId="3" r:id="rId3"/>
+    <sheet name="BD Peluquería" sheetId="5" r:id="rId2"/>
+    <sheet name="Admin" sheetId="2" r:id="rId3"/>
     <sheet name="Trabajadores" sheetId="4" r:id="rId4"/>
+    <sheet name="Clientes" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="182">
   <si>
     <t>v</t>
   </si>
@@ -343,13 +344,244 @@
   </si>
   <si>
     <t>/seguridad/admins/:idadmin</t>
+  </si>
+  <si>
+    <t>Tabla General Peluquería SENA</t>
+  </si>
+  <si>
+    <t>Tabla</t>
+  </si>
+  <si>
+    <t>Filas</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Cotejamiento</t>
+  </si>
+  <si>
+    <t>Tamaño</t>
+  </si>
+  <si>
+    <t>Residuo a depurar</t>
+  </si>
+  <si>
+    <t>clientes</t>
+  </si>
+  <si>
+    <t>InnoDB</t>
+  </si>
+  <si>
+    <t>utf8mb4_general_ci</t>
+  </si>
+  <si>
+    <t>48.0 KB</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>horarios</t>
+  </si>
+  <si>
+    <t>16.0 KB</t>
+  </si>
+  <si>
+    <t>reghorarios</t>
+  </si>
+  <si>
+    <t>trabajadores</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>160.0 KB</t>
+  </si>
+  <si>
+    <t>0 B</t>
+  </si>
+  <si>
+    <t>Estructura Tabla Clientes</t>
+  </si>
+  <si>
+    <t>idCliente</t>
+  </si>
+  <si>
+    <t>tipoDocumento</t>
+  </si>
+  <si>
+    <t>numeroDocumento</t>
+  </si>
+  <si>
+    <t>nombres</t>
+  </si>
+  <si>
+    <t>direccion</t>
+  </si>
+  <si>
+    <t>telefono</t>
+  </si>
+  <si>
+    <t>correo</t>
+  </si>
+  <si>
+    <t>contrasena</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Juan Perez</t>
+  </si>
+  <si>
+    <t>Calle 10 # 20-30</t>
+  </si>
+  <si>
+    <t>juan123@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$NZP...</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>David Tellez</t>
+  </si>
+  <si>
+    <t>cal 1 # 2 4</t>
+  </si>
+  <si>
+    <t>Elmejor@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$.8.C...</t>
+  </si>
+  <si>
+    <t>Cliente Prueba</t>
+  </si>
+  <si>
+    <t>Calle 30 # 30-30</t>
+  </si>
+  <si>
+    <t>cliente@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$oUu1...</t>
+  </si>
+  <si>
+    <t>Cliente Nuevo</t>
+  </si>
+  <si>
+    <t>Calle 30 # 30-38</t>
+  </si>
+  <si>
+    <t>cliente6@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$7mm...</t>
+  </si>
+  <si>
+    <t>cliente67@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$SOn...</t>
+  </si>
+  <si>
+    <t>Estructura Tabla Horarios</t>
+  </si>
+  <si>
+    <t>idHorario</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>horaInicio</t>
+  </si>
+  <si>
+    <t>horaFinal</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>Inactivo</t>
+  </si>
+  <si>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>Estructura Tabla RegHorarios</t>
+  </si>
+  <si>
+    <t>idRegHorario</t>
+  </si>
+  <si>
+    <t>idTrabajador</t>
+  </si>
+  <si>
+    <t>Estructura Tabla Trabajadores</t>
+  </si>
+  <si>
+    <t>Pedro Trabajador</t>
+  </si>
+  <si>
+    <t>Calle 15 # 20-30</t>
+  </si>
+  <si>
+    <t>pedrotrabajador@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$UpFxhnRGoeYF7LOOOWvr1.INE...</t>
+  </si>
+  <si>
+    <t>Maria Gomez</t>
+  </si>
+  <si>
+    <t>Carrera 5 # 10-20</t>
+  </si>
+  <si>
+    <t>mariagomez@gmail.com</t>
+  </si>
+  <si>
+    <t>Guillermo Ortiz</t>
+  </si>
+  <si>
+    <t>cal 1 # 2 3</t>
+  </si>
+  <si>
+    <t>123@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$ZSP8AO5tx.qz06011YBoE...</t>
+  </si>
+  <si>
+    <t>Pepito Perez</t>
+  </si>
+  <si>
+    <t>pepito@gmail.com</t>
+  </si>
+  <si>
+    <t>Admin Prueba</t>
+  </si>
+  <si>
+    <t>Calle 50 # 50-50</t>
+  </si>
+  <si>
+    <t>admin@gmail.com</t>
+  </si>
+  <si>
+    <t>$2b$10$Fx9Vo94gmZzsU/kjmScrCOJ3vY...</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +658,21 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,8 +727,50 @@
         <bgColor rgb="FFF4B084"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -629,11 +916,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -689,6 +991,41 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="14" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="18" fontId="15" fillId="14" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11436,6 +11773,969 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9269433B-3831-4C5D-A934-9A03420A4878}">
+  <dimension ref="A1:K59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="1" width="14.54296875" style="45" customWidth="1"/>
+    <col min="2" max="2" width="17.08984375" style="45" customWidth="1"/>
+    <col min="3" max="3" width="21.6328125" style="45" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" style="45" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" style="45" customWidth="1"/>
+    <col min="6" max="6" width="24.36328125" style="45" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" style="45" customWidth="1"/>
+    <col min="8" max="8" width="41.6328125" style="45" customWidth="1"/>
+    <col min="9" max="16384" width="10.90625" style="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="48">
+        <v>5</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="48">
+        <v>13</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="48">
+        <v>13</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="48">
+        <v>5</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="48">
+        <v>36</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="50">
+        <v>1</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="50">
+        <v>12345678</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="50">
+        <v>3001234567</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="51" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="50">
+        <v>2</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="50">
+        <v>25865254</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="50">
+        <v>3131234569</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="50">
+        <v>3</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="50">
+        <v>33333333</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14" s="50">
+        <v>3030303030</v>
+      </c>
+      <c r="G14" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" s="51" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="50">
+        <v>4</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="50">
+        <v>33333335</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="50">
+        <v>3030303035</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="50">
+        <v>5</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="50">
+        <v>33333355</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="50">
+        <v>3030303035</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="52">
+        <v>1</v>
+      </c>
+      <c r="B21" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D21" s="54">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E21" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="52">
+        <v>2</v>
+      </c>
+      <c r="B22" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C22" s="54">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D22" s="54">
+        <v>0.375</v>
+      </c>
+      <c r="E22" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="52">
+        <v>3</v>
+      </c>
+      <c r="B23" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C23" s="54">
+        <v>0.375</v>
+      </c>
+      <c r="D23" s="54">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E23" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="52">
+        <v>4</v>
+      </c>
+      <c r="B24" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C24" s="54">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D24" s="54">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E24" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="52">
+        <v>5</v>
+      </c>
+      <c r="B25" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C25" s="54">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="52">
+        <v>6</v>
+      </c>
+      <c r="B26" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C26" s="54">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D26" s="54">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E26" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="52">
+        <v>7</v>
+      </c>
+      <c r="B27" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C27" s="54">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D27" s="54">
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="52">
+        <v>8</v>
+      </c>
+      <c r="B28" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C28" s="54">
+        <v>0.625</v>
+      </c>
+      <c r="D28" s="54">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E28" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="52">
+        <v>9</v>
+      </c>
+      <c r="B29" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C29" s="54">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D29" s="54">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E29" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="52">
+        <v>10</v>
+      </c>
+      <c r="B30" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C30" s="54">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D30" s="54">
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="52">
+        <v>11</v>
+      </c>
+      <c r="B31" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C31" s="54">
+        <v>0.75</v>
+      </c>
+      <c r="D31" s="54">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E31" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="52">
+        <v>12</v>
+      </c>
+      <c r="B32" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C32" s="54">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D32" s="54">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E32" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="52">
+        <v>13</v>
+      </c>
+      <c r="B33" s="53">
+        <v>46305</v>
+      </c>
+      <c r="C33" s="54">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D33" s="54">
+        <v>0.875</v>
+      </c>
+      <c r="E33" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="56">
+        <v>1</v>
+      </c>
+      <c r="B38" s="56">
+        <v>1</v>
+      </c>
+      <c r="C38" s="56">
+        <v>1</v>
+      </c>
+      <c r="D38" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="56">
+        <v>2</v>
+      </c>
+      <c r="B39" s="56">
+        <v>2</v>
+      </c>
+      <c r="C39" s="56">
+        <v>1</v>
+      </c>
+      <c r="D39" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="56">
+        <v>3</v>
+      </c>
+      <c r="B40" s="56">
+        <v>3</v>
+      </c>
+      <c r="C40" s="56">
+        <v>1</v>
+      </c>
+      <c r="D40" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="56">
+        <v>4</v>
+      </c>
+      <c r="B41" s="56">
+        <v>4</v>
+      </c>
+      <c r="C41" s="56">
+        <v>1</v>
+      </c>
+      <c r="D41" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="56">
+        <v>5</v>
+      </c>
+      <c r="B42" s="56">
+        <v>5</v>
+      </c>
+      <c r="C42" s="56">
+        <v>1</v>
+      </c>
+      <c r="D42" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="56">
+        <v>6</v>
+      </c>
+      <c r="B43" s="56">
+        <v>6</v>
+      </c>
+      <c r="C43" s="56">
+        <v>1</v>
+      </c>
+      <c r="D43" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="56">
+        <v>7</v>
+      </c>
+      <c r="B44" s="56">
+        <v>7</v>
+      </c>
+      <c r="C44" s="56">
+        <v>1</v>
+      </c>
+      <c r="D44" s="56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="56">
+        <v>8</v>
+      </c>
+      <c r="B45" s="56">
+        <v>8</v>
+      </c>
+      <c r="C45" s="56">
+        <v>1</v>
+      </c>
+      <c r="D45" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="56">
+        <v>9</v>
+      </c>
+      <c r="B46" s="56">
+        <v>9</v>
+      </c>
+      <c r="C46" s="56">
+        <v>1</v>
+      </c>
+      <c r="D46" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="56">
+        <v>10</v>
+      </c>
+      <c r="B47" s="56">
+        <v>10</v>
+      </c>
+      <c r="C47" s="56">
+        <v>1</v>
+      </c>
+      <c r="D47" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="56">
+        <v>11</v>
+      </c>
+      <c r="B48" s="56">
+        <v>11</v>
+      </c>
+      <c r="C48" s="56">
+        <v>1</v>
+      </c>
+      <c r="D48" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="56">
+        <v>12</v>
+      </c>
+      <c r="B49" s="56">
+        <v>12</v>
+      </c>
+      <c r="C49" s="56">
+        <v>1</v>
+      </c>
+      <c r="D49" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="56">
+        <v>13</v>
+      </c>
+      <c r="B50" s="56">
+        <v>13</v>
+      </c>
+      <c r="C50" s="56">
+        <v>1</v>
+      </c>
+      <c r="D50" s="56" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="58" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="F54" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="H54" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="I54" s="59"/>
+      <c r="J54" s="59"/>
+      <c r="K54" s="59"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="56">
+        <v>1</v>
+      </c>
+      <c r="B55" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="56">
+        <v>1098765433</v>
+      </c>
+      <c r="D55" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="F55" s="56">
+        <v>3001234568</v>
+      </c>
+      <c r="G55" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="I55" s="59"/>
+      <c r="J55" s="59"/>
+      <c r="K55" s="59"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="56">
+        <v>2</v>
+      </c>
+      <c r="B56" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" s="56">
+        <v>1098765434</v>
+      </c>
+      <c r="D56" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" s="56">
+        <v>3001234570</v>
+      </c>
+      <c r="G56" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="H56" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="I56" s="59"/>
+      <c r="J56" s="59"/>
+      <c r="K56" s="59"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="56">
+        <v>3</v>
+      </c>
+      <c r="B57" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="56">
+        <v>1070971265</v>
+      </c>
+      <c r="D57" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="E57" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="F57" s="56">
+        <v>3131234567</v>
+      </c>
+      <c r="G57" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="H57" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="I57" s="59"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="59"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="56">
+        <v>4</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="56">
+        <v>1111111111</v>
+      </c>
+      <c r="D58" s="56" t="s">
+        <v>176</v>
+      </c>
+      <c r="E58" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F58" s="56">
+        <v>3131234568</v>
+      </c>
+      <c r="G58" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="H58" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="I58" s="59"/>
+      <c r="J58" s="59"/>
+      <c r="K58" s="59"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="56">
+        <v>5</v>
+      </c>
+      <c r="B59" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="56">
+        <v>55555555</v>
+      </c>
+      <c r="D59" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="F59" s="56">
+        <v>5050505050</v>
+      </c>
+      <c r="G59" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H59" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="I59" s="59"/>
+      <c r="J59" s="59"/>
+      <c r="K59" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A53:H53"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
@@ -12918,25 +14218,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="28.54296875" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="29.7265625" customWidth="1"/>
-    <col min="6" max="6" width="29.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" customWidth="1"/>
-    <col min="8" max="8" width="39.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" customWidth="1"/>
+    <col min="5" max="5" width="36.26953125" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" customWidth="1"/>
     <col min="9" max="26" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
       <c r="A1" s="32" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -12996,160 +14296,110 @@
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>23</v>
+      <c r="H5" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>34</v>
+      <c r="H6" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="A7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="15" t="s">
+      <c r="H7" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1">
-      <c r="A9" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1">
-      <c r="A10" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
+      <c r="H8" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:8" ht="14.25" customHeight="1"/>
@@ -14150,25 +15400,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" customWidth="1"/>
     <col min="2" max="2" width="28.54296875" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" customWidth="1"/>
-    <col min="5" max="5" width="36.26953125" customWidth="1"/>
-    <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="29.7265625" customWidth="1"/>
+    <col min="6" max="6" width="29.453125" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" customWidth="1"/>
+    <col min="8" max="8" width="39.7265625" customWidth="1"/>
     <col min="9" max="26" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
       <c r="A1" s="32" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -14228,110 +15478,160 @@
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>29</v>
+      <c r="H5" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="15" t="s">
+      <c r="H7" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A8" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="21" t="s">
+      <c r="H8" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" customHeight="1"/>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1"/>
+      <c r="H9" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:8" ht="14.25" customHeight="1"/>

--- a/Tabla de endpoints.xlsx
+++ b/Tabla de endpoints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F34AEC-94F5-4962-9A7F-7500F34C6D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06DFCFC-FE3A-4069-833A-EA91A9800613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitácora" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="183">
   <si>
     <t>v</t>
   </si>
@@ -100,9 +100,6 @@
     <t>/trabajador/login</t>
   </si>
   <si>
-    <t>Creado//09102026-se probo funcion ok sn</t>
-  </si>
-  <si>
     <t>vista/Trabajadores/RutasTrabajadores.js</t>
   </si>
   <si>
@@ -575,6 +572,12 @@
   </si>
   <si>
     <t>$2b$10$Fx9Vo94gmZzsU/kjmScrCOJ3vY...</t>
+  </si>
+  <si>
+    <t>Creado 09/10/2026. Función probada OK</t>
+  </si>
+  <si>
+    <t>Creado 12/10/2026. Función probada OK</t>
   </si>
 </sst>
 </file>
@@ -972,31 +975,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1021,11 +999,36 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1256,38 +1259,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:26" ht="15.5">
       <c r="A4" s="1" t="s">
@@ -1335,28 +1338,28 @@
     </row>
     <row r="5" spans="1:26" ht="15.5">
       <c r="A5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.5">
@@ -1382,15 +1385,15 @@
         <v>21</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15.5">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>16</v>
@@ -1399,7 +1402,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>20</v>
@@ -1408,33 +1411,33 @@
         <v>21</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.5">
       <c r="A8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15.5">
@@ -1454,13 +1457,13 @@
         <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I9" s="13"/>
       <c r="K9" s="13"/>
@@ -1482,262 +1485,262 @@
     </row>
     <row r="10" spans="1:26" ht="15.5">
       <c r="A10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.5">
       <c r="A11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="C11" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.5">
       <c r="A12" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.5">
       <c r="A13" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.5">
       <c r="A14" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.5">
       <c r="A15" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.5">
       <c r="A16" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>71</v>
-      </c>
       <c r="C16" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="15.5">
       <c r="A17" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="C17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>74</v>
-      </c>
       <c r="F17" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.5">
       <c r="A18" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="C18" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>77</v>
-      </c>
       <c r="F18" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="G19" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
@@ -1760,28 +1763,28 @@
     </row>
     <row r="20" spans="1:26" ht="14.25" customHeight="1">
       <c r="A20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>60</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
@@ -1804,175 +1807,175 @@
     </row>
     <row r="21" spans="1:26" ht="15.5">
       <c r="A21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="C21" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.5">
       <c r="A22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="C22" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="15.5">
       <c r="A23" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="F23" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="15.5">
       <c r="A24" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="C24" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="F24" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.5">
       <c r="A25" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="C25" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>92</v>
-      </c>
       <c r="F25" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.5">
       <c r="A26" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>95</v>
-      </c>
       <c r="F26" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="15.5">
       <c r="A27" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>20</v>
@@ -1981,85 +1984,85 @@
         <v>21</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.5">
       <c r="A28" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="C28" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>98</v>
-      </c>
       <c r="F28" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.5">
       <c r="A29" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="C29" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>101</v>
-      </c>
       <c r="F29" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.5">
       <c r="A30" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="C30" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>104</v>
-      </c>
       <c r="F30" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="15.5">
@@ -11777,769 +11780,769 @@
   <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" style="45" customWidth="1"/>
-    <col min="2" max="2" width="17.08984375" style="45" customWidth="1"/>
-    <col min="3" max="3" width="21.6328125" style="45" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" style="45" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" style="45" customWidth="1"/>
-    <col min="6" max="6" width="24.36328125" style="45" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="45" customWidth="1"/>
-    <col min="8" max="8" width="41.6328125" style="45" customWidth="1"/>
-    <col min="9" max="16384" width="10.90625" style="45"/>
+    <col min="1" max="1" width="14.54296875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="17.08984375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="21.6328125" style="32" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" style="32" customWidth="1"/>
+    <col min="6" max="6" width="24.36328125" style="32" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="41.6328125" style="32" customWidth="1"/>
+    <col min="9" max="16384" width="10.90625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="46" t="s">
+      <c r="B2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="C2" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="D2" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="E2" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="F2" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="46" t="s">
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="34" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="47" t="s">
+      <c r="B3" s="35">
+        <v>5</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="48">
+      <c r="D3" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="35">
+        <v>13</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="35">
+        <v>13</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="35">
         <v>5</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C6" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="E6" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="F6" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="48">
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="35">
+        <v>36</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="37">
+        <v>1</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="37">
+        <v>12345678</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="37">
+        <v>3001234567</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="37">
+        <v>2</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="37">
+        <v>25865254</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="37">
+        <v>3131234569</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="37">
+        <v>3</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="37">
+        <v>33333333</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" s="37">
+        <v>3030303030</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="37">
+        <v>4</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="37">
+        <v>33333335</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="37">
+        <v>3030303035</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="37">
+        <v>5</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="37">
+        <v>33333355</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" s="37">
+        <v>3030303035</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="39">
+        <v>1</v>
+      </c>
+      <c r="B21" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C21" s="41">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D21" s="41">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="39">
+        <v>2</v>
+      </c>
+      <c r="B22" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C22" s="41">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D22" s="41">
+        <v>0.375</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="39">
+        <v>3</v>
+      </c>
+      <c r="B23" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C23" s="41">
+        <v>0.375</v>
+      </c>
+      <c r="D23" s="41">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="39">
+        <v>4</v>
+      </c>
+      <c r="B24" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C24" s="41">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D24" s="41">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="39">
+        <v>5</v>
+      </c>
+      <c r="B25" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C25" s="41">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="39">
+        <v>6</v>
+      </c>
+      <c r="B26" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C26" s="41">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D26" s="41">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="39">
+        <v>7</v>
+      </c>
+      <c r="B27" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C27" s="41">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D27" s="41">
+        <v>0.625</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="39">
+        <v>8</v>
+      </c>
+      <c r="B28" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C28" s="41">
+        <v>0.625</v>
+      </c>
+      <c r="D28" s="41">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="39">
+        <v>9</v>
+      </c>
+      <c r="B29" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C29" s="41">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D29" s="41">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="39">
+        <v>10</v>
+      </c>
+      <c r="B30" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C30" s="41">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D30" s="41">
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="39">
+        <v>11</v>
+      </c>
+      <c r="B31" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C31" s="41">
+        <v>0.75</v>
+      </c>
+      <c r="D31" s="41">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="39">
+        <v>12</v>
+      </c>
+      <c r="B32" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C32" s="41">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D32" s="41">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="39">
         <v>13</v>
       </c>
-      <c r="C4" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="48">
+      <c r="B33" s="40">
+        <v>46305</v>
+      </c>
+      <c r="C33" s="41">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D33" s="41">
+        <v>0.875</v>
+      </c>
+      <c r="E33" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="43">
+        <v>1</v>
+      </c>
+      <c r="B38" s="43">
+        <v>1</v>
+      </c>
+      <c r="C38" s="43">
+        <v>1</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="43">
+        <v>2</v>
+      </c>
+      <c r="B39" s="43">
+        <v>2</v>
+      </c>
+      <c r="C39" s="43">
+        <v>1</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="43">
+        <v>3</v>
+      </c>
+      <c r="B40" s="43">
+        <v>3</v>
+      </c>
+      <c r="C40" s="43">
+        <v>1</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="43">
+        <v>4</v>
+      </c>
+      <c r="B41" s="43">
+        <v>4</v>
+      </c>
+      <c r="C41" s="43">
+        <v>1</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="43">
+        <v>5</v>
+      </c>
+      <c r="B42" s="43">
+        <v>5</v>
+      </c>
+      <c r="C42" s="43">
+        <v>1</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="43">
+        <v>6</v>
+      </c>
+      <c r="B43" s="43">
+        <v>6</v>
+      </c>
+      <c r="C43" s="43">
+        <v>1</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="43">
+        <v>7</v>
+      </c>
+      <c r="B44" s="43">
+        <v>7</v>
+      </c>
+      <c r="C44" s="43">
+        <v>1</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="43">
+        <v>8</v>
+      </c>
+      <c r="B45" s="43">
+        <v>8</v>
+      </c>
+      <c r="C45" s="43">
+        <v>1</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="43">
+        <v>9</v>
+      </c>
+      <c r="B46" s="43">
+        <v>9</v>
+      </c>
+      <c r="C46" s="43">
+        <v>1</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="43">
+        <v>10</v>
+      </c>
+      <c r="B47" s="43">
+        <v>10</v>
+      </c>
+      <c r="C47" s="43">
+        <v>1</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="43">
+        <v>11</v>
+      </c>
+      <c r="B48" s="43">
+        <v>11</v>
+      </c>
+      <c r="C48" s="43">
+        <v>1</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="43">
+        <v>12</v>
+      </c>
+      <c r="B49" s="43">
+        <v>12</v>
+      </c>
+      <c r="C49" s="43">
+        <v>1</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="43">
         <v>13</v>
       </c>
-      <c r="C5" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="48">
-        <v>5</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="48">
-        <v>36</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="47" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="50">
+      <c r="B50" s="43">
+        <v>13</v>
+      </c>
+      <c r="C50" s="43">
         <v>1</v>
       </c>
-      <c r="B12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="50">
-        <v>12345678</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="F12" s="50">
-        <v>3001234567</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="51" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="50">
-        <v>2</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="50">
-        <v>25865254</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" s="50">
-        <v>3131234569</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="H13" s="51" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="50">
-        <v>3</v>
-      </c>
-      <c r="B14" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="50">
-        <v>33333333</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="F14" s="50">
-        <v>3030303030</v>
-      </c>
-      <c r="G14" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="H14" s="51" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="50">
-        <v>4</v>
-      </c>
-      <c r="B15" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="50">
-        <v>33333335</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="F15" s="50">
-        <v>3030303035</v>
-      </c>
-      <c r="G15" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" s="51" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="50">
-        <v>5</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="50">
-        <v>33333355</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="50">
-        <v>3030303035</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="51" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="B20" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="52">
-        <v>1</v>
-      </c>
-      <c r="B21" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C21" s="54">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D21" s="54">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E21" s="55" t="s">
+      <c r="D50" s="43" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="52">
-        <v>2</v>
-      </c>
-      <c r="B22" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C22" s="54">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D22" s="54">
-        <v>0.375</v>
-      </c>
-      <c r="E22" s="55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="52">
-        <v>3</v>
-      </c>
-      <c r="B23" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C23" s="54">
-        <v>0.375</v>
-      </c>
-      <c r="D23" s="54">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E23" s="55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="52">
-        <v>4</v>
-      </c>
-      <c r="B24" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C24" s="54">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D24" s="54">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E24" s="55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="52">
-        <v>5</v>
-      </c>
-      <c r="B25" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C25" s="54">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="52">
-        <v>6</v>
-      </c>
-      <c r="B26" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C26" s="54">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D26" s="54">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E26" s="55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="52">
-        <v>7</v>
-      </c>
-      <c r="B27" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C27" s="54">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D27" s="54">
-        <v>0.625</v>
-      </c>
-      <c r="E27" s="55" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="52">
-        <v>8</v>
-      </c>
-      <c r="B28" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C28" s="54">
-        <v>0.625</v>
-      </c>
-      <c r="D28" s="54">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E28" s="55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="52">
-        <v>9</v>
-      </c>
-      <c r="B29" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C29" s="54">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D29" s="54">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E29" s="55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="52">
-        <v>10</v>
-      </c>
-      <c r="B30" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C30" s="54">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D30" s="54">
-        <v>0.75</v>
-      </c>
-      <c r="E30" s="55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="52">
-        <v>11</v>
-      </c>
-      <c r="B31" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C31" s="54">
-        <v>0.75</v>
-      </c>
-      <c r="D31" s="54">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E31" s="55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="52">
-        <v>12</v>
-      </c>
-      <c r="B32" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C32" s="54">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D32" s="54">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E32" s="55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="52">
-        <v>13</v>
-      </c>
-      <c r="B33" s="53">
-        <v>46305</v>
-      </c>
-      <c r="C33" s="54">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D33" s="54">
-        <v>0.875</v>
-      </c>
-      <c r="E33" s="55" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="B37" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="56">
-        <v>1</v>
-      </c>
-      <c r="B38" s="56">
-        <v>1</v>
-      </c>
-      <c r="C38" s="56">
-        <v>1</v>
-      </c>
-      <c r="D38" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="56">
-        <v>2</v>
-      </c>
-      <c r="B39" s="56">
-        <v>2</v>
-      </c>
-      <c r="C39" s="56">
-        <v>1</v>
-      </c>
-      <c r="D39" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="56">
-        <v>3</v>
-      </c>
-      <c r="B40" s="56">
-        <v>3</v>
-      </c>
-      <c r="C40" s="56">
-        <v>1</v>
-      </c>
-      <c r="D40" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="56">
-        <v>4</v>
-      </c>
-      <c r="B41" s="56">
-        <v>4</v>
-      </c>
-      <c r="C41" s="56">
-        <v>1</v>
-      </c>
-      <c r="D41" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="56">
-        <v>5</v>
-      </c>
-      <c r="B42" s="56">
-        <v>5</v>
-      </c>
-      <c r="C42" s="56">
-        <v>1</v>
-      </c>
-      <c r="D42" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="56">
-        <v>6</v>
-      </c>
-      <c r="B43" s="56">
-        <v>6</v>
-      </c>
-      <c r="C43" s="56">
-        <v>1</v>
-      </c>
-      <c r="D43" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="56">
-        <v>7</v>
-      </c>
-      <c r="B44" s="56">
-        <v>7</v>
-      </c>
-      <c r="C44" s="56">
-        <v>1</v>
-      </c>
-      <c r="D44" s="56" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="56">
-        <v>8</v>
-      </c>
-      <c r="B45" s="56">
-        <v>8</v>
-      </c>
-      <c r="C45" s="56">
-        <v>1</v>
-      </c>
-      <c r="D45" s="56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="56">
-        <v>9</v>
-      </c>
-      <c r="B46" s="56">
-        <v>9</v>
-      </c>
-      <c r="C46" s="56">
-        <v>1</v>
-      </c>
-      <c r="D46" s="56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="56">
-        <v>10</v>
-      </c>
-      <c r="B47" s="56">
-        <v>10</v>
-      </c>
-      <c r="C47" s="56">
-        <v>1</v>
-      </c>
-      <c r="D47" s="56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="56">
-        <v>11</v>
-      </c>
-      <c r="B48" s="56">
-        <v>11</v>
-      </c>
-      <c r="C48" s="56">
-        <v>1</v>
-      </c>
-      <c r="D48" s="56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="56">
-        <v>12</v>
-      </c>
-      <c r="B49" s="56">
-        <v>12</v>
-      </c>
-      <c r="C49" s="56">
-        <v>1</v>
-      </c>
-      <c r="D49" s="56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="56">
-        <v>13</v>
-      </c>
-      <c r="B50" s="56">
-        <v>13</v>
-      </c>
-      <c r="C50" s="56">
-        <v>1</v>
-      </c>
-      <c r="D50" s="56" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B53" s="57"/>
       <c r="C53" s="57"/>
@@ -12550,178 +12553,178 @@
       <c r="H53" s="57"/>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" s="58" t="s">
+      <c r="A54" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="D54" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="D54" s="58" t="s">
+      <c r="E54" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="E54" s="58" t="s">
+      <c r="F54" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="F54" s="58" t="s">
+      <c r="G54" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="G54" s="58" t="s">
+      <c r="H54" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="H54" s="58" t="s">
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="43">
+        <v>1</v>
+      </c>
+      <c r="B55" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="I54" s="59"/>
-      <c r="J54" s="59"/>
-      <c r="K54" s="59"/>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="56">
-        <v>1</v>
-      </c>
-      <c r="B55" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C55" s="56">
+      <c r="C55" s="43">
         <v>1098765433</v>
       </c>
-      <c r="D55" s="56" t="s">
+      <c r="D55" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="E55" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="56" t="s">
+      <c r="F55" s="43">
+        <v>3001234568</v>
+      </c>
+      <c r="G55" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="F55" s="56">
-        <v>3001234568</v>
-      </c>
-      <c r="G55" s="56" t="s">
+      <c r="H55" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="H55" s="56" t="s">
+      <c r="I55" s="45"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="43">
+        <v>2</v>
+      </c>
+      <c r="B56" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="43">
+        <v>1098765434</v>
+      </c>
+      <c r="D56" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="59"/>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="56">
-        <v>2</v>
-      </c>
-      <c r="B56" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C56" s="56">
-        <v>1098765434</v>
-      </c>
-      <c r="D56" s="56" t="s">
+      <c r="E56" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="E56" s="56" t="s">
+      <c r="F56" s="43">
+        <v>3001234570</v>
+      </c>
+      <c r="G56" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="F56" s="56">
-        <v>3001234570</v>
-      </c>
-      <c r="G56" s="56" t="s">
+      <c r="H56" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="I56" s="45"/>
+      <c r="J56" s="45"/>
+      <c r="K56" s="45"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="43">
+        <v>3</v>
+      </c>
+      <c r="B57" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="43">
+        <v>1070971265</v>
+      </c>
+      <c r="D57" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="H56" s="56" t="s">
-        <v>168</v>
-      </c>
-      <c r="I56" s="59"/>
-      <c r="J56" s="59"/>
-      <c r="K56" s="59"/>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="56">
-        <v>3</v>
-      </c>
-      <c r="B57" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C57" s="56">
-        <v>1070971265</v>
-      </c>
-      <c r="D57" s="56" t="s">
+      <c r="E57" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="E57" s="56" t="s">
+      <c r="F57" s="43">
+        <v>3131234567</v>
+      </c>
+      <c r="G57" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="F57" s="56">
-        <v>3131234567</v>
-      </c>
-      <c r="G57" s="56" t="s">
+      <c r="H57" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="H57" s="56" t="s">
+      <c r="I57" s="45"/>
+      <c r="J57" s="45"/>
+      <c r="K57" s="45"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="43">
+        <v>4</v>
+      </c>
+      <c r="B58" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="43">
+        <v>1111111111</v>
+      </c>
+      <c r="D58" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="I57" s="59"/>
-      <c r="J57" s="59"/>
-      <c r="K57" s="59"/>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" s="56">
-        <v>4</v>
-      </c>
-      <c r="B58" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="56">
-        <v>1111111111</v>
-      </c>
-      <c r="D58" s="56" t="s">
+      <c r="E58" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="F58" s="43">
+        <v>3131234568</v>
+      </c>
+      <c r="G58" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="E58" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F58" s="56">
-        <v>3131234568</v>
-      </c>
-      <c r="G58" s="56" t="s">
+      <c r="H58" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="I58" s="45"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="43">
+        <v>5</v>
+      </c>
+      <c r="B59" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="43">
+        <v>55555555</v>
+      </c>
+      <c r="D59" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="H58" s="56" t="s">
-        <v>168</v>
-      </c>
-      <c r="I58" s="59"/>
-      <c r="J58" s="59"/>
-      <c r="K58" s="59"/>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" s="56">
-        <v>5</v>
-      </c>
-      <c r="B59" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="56">
-        <v>55555555</v>
-      </c>
-      <c r="D59" s="56" t="s">
+      <c r="E59" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="E59" s="56" t="s">
+      <c r="F59" s="43">
+        <v>5050505050</v>
+      </c>
+      <c r="G59" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="F59" s="56">
-        <v>5050505050</v>
-      </c>
-      <c r="G59" s="56" t="s">
+      <c r="H59" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="H59" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="I59" s="59"/>
-      <c r="J59" s="59"/>
-      <c r="K59" s="59"/>
+      <c r="I59" s="45"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12741,49 +12744,49 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="35.26953125" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" customWidth="1"/>
     <col min="3" max="3" width="15.08984375" customWidth="1"/>
     <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="42.26953125" customWidth="1"/>
+    <col min="5" max="5" width="37.7265625" customWidth="1"/>
     <col min="6" max="6" width="28.26953125" customWidth="1"/>
     <col min="7" max="7" width="12.81640625" customWidth="1"/>
-    <col min="8" max="8" width="42.08984375" customWidth="1"/>
+    <col min="8" max="8" width="38.54296875" customWidth="1"/>
     <col min="9" max="26" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -12813,419 +12816,419 @@
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1">
       <c r="A6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>43</v>
-      </c>
       <c r="C6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1">
       <c r="A7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>47</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1">
       <c r="A9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>71</v>
-      </c>
       <c r="C9" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1">
       <c r="A10" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="C10" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>74</v>
-      </c>
       <c r="F10" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1">
       <c r="A11" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="C11" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>77</v>
-      </c>
       <c r="F11" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.25" customHeight="1">
       <c r="A12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="C12" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1">
       <c r="A13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="C13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
       <c r="A14" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="C14" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>86</v>
-      </c>
       <c r="F14" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="C15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>89</v>
-      </c>
       <c r="F15" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="C16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>92</v>
-      </c>
       <c r="F16" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="C17" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>95</v>
-      </c>
       <c r="F17" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="C18" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>98</v>
-      </c>
       <c r="F18" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="C19" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>101</v>
-      </c>
       <c r="F19" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1">
       <c r="A20" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="C20" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>104</v>
-      </c>
       <c r="F20" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1"/>
@@ -14235,38 +14238,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -14311,91 +14314,91 @@
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1"/>
@@ -15417,38 +15420,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -15499,15 +15502,15 @@
         <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>16</v>
@@ -15516,7 +15519,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>20</v>
@@ -15525,102 +15528,102 @@
         <v>21</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>60</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>20</v>
@@ -15629,7 +15632,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1"/>

--- a/Tabla de endpoints.xlsx
+++ b/Tabla de endpoints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06DFCFC-FE3A-4069-833A-EA91A9800613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D4D87-0AF2-4226-A95C-B097D9A8D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitácora" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="189">
   <si>
     <t>v</t>
   </si>
@@ -100,9 +100,6 @@
     <t>/trabajador/login</t>
   </si>
   <si>
-    <t>vista/Trabajadores/RutasTrabajadores.js</t>
-  </si>
-  <si>
     <t>RF - 01</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>/seguridad/crearcliente</t>
   </si>
   <si>
-    <t>RF - 08</t>
-  </si>
-  <si>
     <t>Creado//PTE POR ´PRUEBAS</t>
   </si>
   <si>
@@ -160,9 +154,6 @@
     <t xml:space="preserve">Admin crea trabajador </t>
   </si>
   <si>
-    <t>/trabajador/horarios/:idtrabajador</t>
-  </si>
-  <si>
     <t>/seguridad/creartrabajador</t>
   </si>
   <si>
@@ -187,9 +178,6 @@
     <t>Cliente cancela una cita</t>
   </si>
   <si>
-    <t>/horarios/:idhorario</t>
-  </si>
-  <si>
     <t>PUT</t>
   </si>
   <si>
@@ -578,6 +566,36 @@
   </si>
   <si>
     <t>Creado 12/10/2026. Función probada OK</t>
+  </si>
+  <si>
+    <t>Creado 13/10/2026. Función probada OK</t>
+  </si>
+  <si>
+    <t>/trabajador/horariod/:id&amp;:fecha</t>
+  </si>
+  <si>
+    <t>/trabajador/horarioe/:id&amp;:fecha&amp;:est</t>
+  </si>
+  <si>
+    <t>RF - 08.1</t>
+  </si>
+  <si>
+    <t>RF - 08.2</t>
+  </si>
+  <si>
+    <t>RF - 08.3</t>
+  </si>
+  <si>
+    <t>vista/trabajadores/RutasTrabajadores.js</t>
+  </si>
+  <si>
+    <t>Trabajador ve sus horarios</t>
+  </si>
+  <si>
+    <t>/trabajador/horariot/:id</t>
+  </si>
+  <si>
+    <t>Creado 14/10/2026. Función probada OK</t>
   </si>
 </sst>
 </file>
@@ -938,7 +956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1029,6 +1047,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.54296875" customWidth="1"/>
@@ -1338,28 +1357,28 @@
     </row>
     <row r="5" spans="1:26" ht="15.5">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.5">
@@ -1385,15 +1404,15 @@
         <v>21</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15.5">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>16</v>
@@ -1402,7 +1421,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>20</v>
@@ -1411,33 +1430,33 @@
         <v>21</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.5">
       <c r="A8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15.5">
@@ -1457,13 +1476,13 @@
         <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9" s="13"/>
       <c r="K9" s="13"/>
@@ -1485,605 +1504,629 @@
     </row>
     <row r="10" spans="1:26" ht="15.5">
       <c r="A10" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.5">
       <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.5">
       <c r="A12" s="7" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.5">
-      <c r="A13" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="15" t="s">
+      <c r="D13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>28</v>
+      <c r="H13" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.5">
-      <c r="A14" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="21" t="s">
+      <c r="A14" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="D14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="21" t="s">
-        <v>28</v>
+      <c r="H14" s="60" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.5">
       <c r="A15" s="15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>34</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.5">
       <c r="A16" s="21" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="21" t="s">
-        <v>34</v>
-      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="15.5">
+      <c r="A17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" ht="15.5">
-      <c r="A17" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="21" t="s">
+      <c r="D17" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="21" t="s">
-        <v>28</v>
+      <c r="H17" s="15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.5">
       <c r="A18" s="21" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15.5">
+      <c r="A19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="17" t="s">
+      <c r="D19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="15.5">
+      <c r="A20" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="F21" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="28"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="28"/>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="28"/>
+    </row>
+    <row r="22" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="15" t="s">
+      <c r="D22" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="28"/>
+    </row>
+    <row r="23" spans="1:26" ht="15.5">
+      <c r="A23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-    </row>
-    <row r="20" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="15" t="s">
+      <c r="D23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H23" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="15.5">
+      <c r="A24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-    </row>
-    <row r="21" spans="1:26" ht="15.5">
-      <c r="A21" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="F24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" ht="15.5">
-      <c r="A22" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="15.5">
-      <c r="A23" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="15.5">
-      <c r="A24" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>28</v>
+      <c r="H24" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.5">
       <c r="A25" s="15" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.5">
       <c r="A26" s="15" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="15" t="s">
-        <v>28</v>
+      <c r="H26" s="19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="15.5">
       <c r="A27" s="15" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G27" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.5">
       <c r="A28" s="15" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.5">
       <c r="A29" s="15" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G29" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" ht="15.5">
+      <c r="A30" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" ht="15.5">
-      <c r="A30" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30" s="21" t="s">
+      <c r="D30" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" ht="15.5">
+      <c r="A31" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" ht="15.5">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="31"/>
+      <c r="D31" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="32" spans="1:26" ht="15.5">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="31"/>
+      <c r="A32" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="15.5">
       <c r="A33" s="30"/>
@@ -11764,6 +11807,26 @@
       <c r="F1000" s="31"/>
       <c r="G1000" s="30"/>
       <c r="H1000" s="31"/>
+    </row>
+    <row r="1001" spans="1:8" ht="15.5">
+      <c r="A1001" s="30"/>
+      <c r="B1001" s="30"/>
+      <c r="C1001" s="30"/>
+      <c r="D1001" s="30"/>
+      <c r="E1001" s="31"/>
+      <c r="F1001" s="31"/>
+      <c r="G1001" s="30"/>
+      <c r="H1001" s="31"/>
+    </row>
+    <row r="1002" spans="1:8" ht="15.5">
+      <c r="A1002" s="30"/>
+      <c r="B1002" s="30"/>
+      <c r="C1002" s="30"/>
+      <c r="D1002" s="30"/>
+      <c r="E1002" s="31"/>
+      <c r="F1002" s="31"/>
+      <c r="G1002" s="30"/>
+      <c r="H1002" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11793,7 +11856,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="55" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -11803,127 +11866,127 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>106</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="34" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B3" s="35">
         <v>5</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="34" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B4" s="35">
         <v>13</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D4" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>117</v>
-      </c>
       <c r="F4" s="34" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="34" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B5" s="35">
         <v>13</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B6" s="35">
         <v>5</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="34" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B7" s="35">
         <v>36</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="55" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B10" s="55"/>
       <c r="C10" s="55"/>
@@ -11935,28 +11998,28 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="F11" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="G11" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="H11" s="36" t="s">
         <v>127</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -11964,25 +12027,25 @@
         <v>1</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C12" s="37">
         <v>12345678</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F12" s="37">
         <v>3001234567</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -11990,25 +12053,25 @@
         <v>2</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C13" s="37">
         <v>25865254</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F13" s="37">
         <v>3131234569</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -12016,25 +12079,25 @@
         <v>3</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C14" s="37">
         <v>33333333</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F14" s="37">
         <v>3030303030</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12042,25 +12105,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C15" s="37">
         <v>33333335</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F15" s="37">
         <v>3030303035</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -12068,30 +12131,30 @@
         <v>5</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C16" s="37">
         <v>33333355</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F16" s="37">
         <v>3030303035</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="55" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B19" s="55"/>
       <c r="C19" s="55"/>
@@ -12100,19 +12163,19 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>153</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -12129,7 +12192,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -12146,7 +12209,7 @@
         <v>0.375</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -12163,7 +12226,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -12180,7 +12243,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -12197,7 +12260,7 @@
         <v>0.5</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -12214,7 +12277,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -12231,7 +12294,7 @@
         <v>0.625</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -12248,7 +12311,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -12265,7 +12328,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -12282,7 +12345,7 @@
         <v>0.75</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -12299,7 +12362,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -12316,7 +12379,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -12333,12 +12396,12 @@
         <v>0.875</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="55" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B36" s="55"/>
       <c r="C36" s="55"/>
@@ -12346,16 +12409,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="36" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B37" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="36" t="s">
         <v>153</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -12369,7 +12432,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -12383,7 +12446,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -12397,7 +12460,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -12411,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -12425,7 +12488,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -12439,7 +12502,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -12453,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -12467,7 +12530,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -12481,7 +12544,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -12495,7 +12558,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -12509,7 +12572,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -12523,7 +12586,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -12537,12 +12600,12 @@
         <v>1</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="57" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B53" s="57"/>
       <c r="C53" s="57"/>
@@ -12554,28 +12617,28 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="44" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B54" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="E54" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F54" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="G54" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="H54" s="44" t="s">
         <v>127</v>
-      </c>
-      <c r="E54" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="F54" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="G54" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H54" s="44" t="s">
-        <v>131</v>
       </c>
       <c r="I54" s="45"/>
       <c r="J54" s="45"/>
@@ -12586,25 +12649,25 @@
         <v>1</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C55" s="43">
         <v>1098765433</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F55" s="43">
         <v>3001234568</v>
       </c>
       <c r="G55" s="43" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H55" s="43" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I55" s="45"/>
       <c r="J55" s="45"/>
@@ -12615,25 +12678,25 @@
         <v>2</v>
       </c>
       <c r="B56" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C56" s="43">
         <v>1098765434</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F56" s="43">
         <v>3001234570</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H56" s="43" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I56" s="45"/>
       <c r="J56" s="45"/>
@@ -12644,25 +12707,25 @@
         <v>3</v>
       </c>
       <c r="B57" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C57" s="43">
         <v>1070971265</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F57" s="43">
         <v>3131234567</v>
       </c>
       <c r="G57" s="43" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H57" s="43" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I57" s="45"/>
       <c r="J57" s="45"/>
@@ -12673,25 +12736,25 @@
         <v>4</v>
       </c>
       <c r="B58" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C58" s="43">
         <v>1111111111</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E58" s="43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F58" s="43">
         <v>3131234568</v>
       </c>
       <c r="G58" s="43" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I58" s="45"/>
       <c r="J58" s="45"/>
@@ -12702,25 +12765,25 @@
         <v>5</v>
       </c>
       <c r="B59" s="43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C59" s="43">
         <v>55555555</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E59" s="43" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F59" s="43">
         <v>5050505050</v>
       </c>
       <c r="G59" s="43" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H59" s="43" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I59" s="45"/>
       <c r="J59" s="45"/>
@@ -12816,419 +12879,419 @@
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>49</v>
-      </c>
       <c r="F7" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B8" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>61</v>
-      </c>
       <c r="F8" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1">
       <c r="A9" s="24" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1">
       <c r="A10" s="24" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1">
       <c r="A11" s="24" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.25" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1">
       <c r="A20" s="24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G20" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1"/>
@@ -14223,17 +14286,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="28.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.54296875" customWidth="1"/>
     <col min="4" max="4" width="18.453125" customWidth="1"/>
-    <col min="5" max="5" width="36.26953125" customWidth="1"/>
+    <col min="5" max="5" width="42.6328125" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
     <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="20.453125" customWidth="1"/>
+    <col min="8" max="8" width="39.36328125" customWidth="1"/>
     <col min="9" max="26" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14314,96 +14377,138 @@
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>28</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G6" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>28</v>
+      <c r="H6" s="60" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="15" t="s">
+      <c r="D7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>28</v>
+      <c r="H7" s="60" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A8" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="21" t="s">
+      <c r="A8" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="21" t="s">
+      <c r="D8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="13.5" customHeight="1"/>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1"/>
+      <c r="H8" s="60" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" customHeight="1"/>
     <row r="12" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:8" ht="14.25" customHeight="1"/>
@@ -15393,13 +15498,15 @@
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="1001" ht="14.25" customHeight="1"/>
+    <row r="1002" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15502,15 +15609,15 @@
         <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>16</v>
@@ -15519,7 +15626,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>20</v>
@@ -15528,102 +15635,102 @@
         <v>21</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>20</v>
@@ -15632,7 +15739,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1"/>

--- a/Tabla de endpoints.xlsx
+++ b/Tabla de endpoints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5D4D87-0AF2-4226-A95C-B097D9A8D25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E5B6B-F2CD-4A1A-98EE-13EFD74C9F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="190">
   <si>
     <t>v</t>
   </si>
@@ -118,9 +118,6 @@
     <t>Administrador</t>
   </si>
   <si>
-    <t>/login</t>
-  </si>
-  <si>
     <t>/seguridad/crearcliente</t>
   </si>
   <si>
@@ -596,6 +593,12 @@
   </si>
   <si>
     <t>Creado 14/10/2026. Función probada OK</t>
+  </si>
+  <si>
+    <t>/cliente/login</t>
+  </si>
+  <si>
+    <t>Creado 18/10/2026. Función probada OK</t>
   </si>
 </sst>
 </file>
@@ -1019,6 +1022,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1047,7 +1051,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1278,38 +1281,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:26" ht="15.5">
       <c r="A4" s="1" t="s">
@@ -1369,10 +1372,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
@@ -1421,7 +1424,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>20</v>
@@ -1435,10 +1438,10 @@
     </row>
     <row r="8" spans="1:26" ht="15.5">
       <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>28</v>
@@ -1447,10 +1450,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>21</v>
@@ -1476,7 +1479,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>21</v>
@@ -1504,22 +1507,22 @@
     </row>
     <row r="10" spans="1:26" ht="15.5">
       <c r="A10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>21</v>
@@ -1530,22 +1533,22 @@
     </row>
     <row r="11" spans="1:26" ht="15.5">
       <c r="A11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>21</v>
@@ -1556,22 +1559,22 @@
     </row>
     <row r="12" spans="1:26" ht="15.5">
       <c r="A12" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>21</v>
@@ -1582,22 +1585,22 @@
     </row>
     <row r="13" spans="1:26" ht="15.5">
       <c r="A13" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F13" s="60" t="s">
-        <v>185</v>
+        <v>180</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>184</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>21</v>
@@ -1608,42 +1611,42 @@
     </row>
     <row r="14" spans="1:26" ht="15.5">
       <c r="A14" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>187</v>
-      </c>
-      <c r="F14" s="60" t="s">
-        <v>185</v>
-      </c>
-      <c r="G14" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="60" t="s">
+      <c r="H14" s="46" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.5">
       <c r="A15" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
@@ -1656,16 +1659,16 @@
     </row>
     <row r="16" spans="1:26" ht="15.5">
       <c r="A16" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -1678,22 +1681,22 @@
     </row>
     <row r="17" spans="1:26" ht="15.5">
       <c r="A17" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>21</v>
@@ -1704,22 +1707,22 @@
     </row>
     <row r="18" spans="1:26" ht="15.5">
       <c r="A18" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>65</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>66</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>21</v>
@@ -1730,22 +1733,22 @@
     </row>
     <row r="19" spans="1:26" ht="15.5">
       <c r="A19" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="21" t="s">
         <v>21</v>
@@ -1756,22 +1759,22 @@
     </row>
     <row r="20" spans="1:26" ht="15.5">
       <c r="A20" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>70</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>71</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>21</v>
@@ -1782,22 +1785,22 @@
     </row>
     <row r="21" spans="1:26" ht="14.25" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>52</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>21</v>
@@ -1826,22 +1829,22 @@
     </row>
     <row r="22" spans="1:26" ht="14.25" customHeight="1">
       <c r="A22" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>55</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" s="15" t="s">
         <v>21</v>
@@ -1870,10 +1873,10 @@
     </row>
     <row r="23" spans="1:26" ht="15.5">
       <c r="A23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>28</v>
@@ -1882,10 +1885,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>21</v>
@@ -1896,10 +1899,10 @@
     </row>
     <row r="24" spans="1:26" ht="15.5">
       <c r="A24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>28</v>
@@ -1908,10 +1911,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>21</v>
@@ -1922,22 +1925,22 @@
     </row>
     <row r="25" spans="1:26" ht="15.5">
       <c r="A25" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>79</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>80</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>21</v>
@@ -1948,22 +1951,22 @@
     </row>
     <row r="26" spans="1:26" ht="15.5">
       <c r="A26" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>82</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>83</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>21</v>
@@ -1974,22 +1977,22 @@
     </row>
     <row r="27" spans="1:26" ht="15.5">
       <c r="A27" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>85</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>86</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" s="15" t="s">
         <v>21</v>
@@ -2000,22 +2003,22 @@
     </row>
     <row r="28" spans="1:26" ht="15.5">
       <c r="A28" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>88</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>89</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>21</v>
@@ -2026,19 +2029,19 @@
     </row>
     <row r="29" spans="1:26" ht="15.5">
       <c r="A29" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>20</v>
@@ -2052,22 +2055,22 @@
     </row>
     <row r="30" spans="1:26" ht="15.5">
       <c r="A30" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="17" t="s">
         <v>91</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>92</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" s="15" t="s">
         <v>21</v>
@@ -2078,22 +2081,22 @@
     </row>
     <row r="31" spans="1:26" ht="15.5">
       <c r="A31" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>94</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>95</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" s="15" t="s">
         <v>21</v>
@@ -2104,22 +2107,22 @@
     </row>
     <row r="32" spans="1:26" ht="15.5">
       <c r="A32" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>97</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="C32" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G32" s="21" t="s">
         <v>21</v>
@@ -11855,171 +11858,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="A1" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="C2" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="D2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="E2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>105</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" s="35">
         <v>5</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="E3" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="F3" s="34" t="s">
         <v>110</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="35">
         <v>13</v>
       </c>
       <c r="C4" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>109</v>
-      </c>
       <c r="E4" s="34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="35">
         <v>13</v>
       </c>
       <c r="C5" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="E5" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="F5" s="34" t="s">
         <v>110</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" s="35">
         <v>5</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="E6" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="F6" s="34" t="s">
         <v>110</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" s="35">
         <v>36</v>
       </c>
       <c r="C7" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="34" t="s">
-        <v>109</v>
-      </c>
       <c r="E7" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="F7" s="34" t="s">
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="56" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="C11" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="E11" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="F11" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="G11" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="H11" s="36" t="s">
         <v>126</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -12027,25 +12030,25 @@
         <v>1</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="37">
         <v>12345678</v>
       </c>
       <c r="D12" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="38" t="s">
         <v>129</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>130</v>
       </c>
       <c r="F12" s="37">
         <v>3001234567</v>
       </c>
       <c r="G12" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>131</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -12053,25 +12056,25 @@
         <v>2</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C13" s="37">
         <v>25865254</v>
       </c>
       <c r="D13" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="38" t="s">
         <v>134</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>135</v>
       </c>
       <c r="F13" s="37">
         <v>3131234569</v>
       </c>
       <c r="G13" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="38" t="s">
         <v>136</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -12079,25 +12082,25 @@
         <v>3</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="37">
         <v>33333333</v>
       </c>
       <c r="D14" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="38" t="s">
         <v>138</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>139</v>
       </c>
       <c r="F14" s="37">
         <v>3030303030</v>
       </c>
       <c r="G14" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" s="38" t="s">
         <v>140</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12105,25 +12108,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" s="37">
         <v>33333335</v>
       </c>
       <c r="D15" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="38" t="s">
         <v>142</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>143</v>
       </c>
       <c r="F15" s="37">
         <v>3030303035</v>
       </c>
       <c r="G15" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="H15" s="38" t="s">
         <v>144</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -12131,51 +12134,51 @@
         <v>5</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" s="37">
         <v>33333355</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F16" s="37">
         <v>3030303035</v>
       </c>
       <c r="G16" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="H16" s="38" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="56" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="C20" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="D20" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>152</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -12192,7 +12195,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -12209,7 +12212,7 @@
         <v>0.375</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -12226,7 +12229,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -12243,7 +12246,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -12260,7 +12263,7 @@
         <v>0.5</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -12277,7 +12280,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -12294,7 +12297,7 @@
         <v>0.625</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -12311,7 +12314,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -12328,7 +12331,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -12345,7 +12348,7 @@
         <v>0.75</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -12362,7 +12365,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -12379,7 +12382,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -12396,29 +12399,29 @@
         <v>0.875</v>
       </c>
       <c r="E33" s="42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="56" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="55" t="s">
-        <v>156</v>
-      </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="B37" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>158</v>
-      </c>
       <c r="D37" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -12432,7 +12435,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -12446,7 +12449,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -12460,7 +12463,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -12474,7 +12477,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -12488,7 +12491,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -12502,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -12516,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -12530,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -12544,7 +12547,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -12558,7 +12561,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -12572,7 +12575,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -12586,7 +12589,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -12600,45 +12603,45 @@
         <v>1</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
+      <c r="A53" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B54" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="D54" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="E54" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="E54" s="44" t="s">
+      <c r="F54" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="F54" s="44" t="s">
+      <c r="G54" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="G54" s="44" t="s">
+      <c r="H54" s="44" t="s">
         <v>126</v>
-      </c>
-      <c r="H54" s="44" t="s">
-        <v>127</v>
       </c>
       <c r="I54" s="45"/>
       <c r="J54" s="45"/>
@@ -12649,25 +12652,25 @@
         <v>1</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C55" s="43">
         <v>1098765433</v>
       </c>
       <c r="D55" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" s="43" t="s">
         <v>160</v>
-      </c>
-      <c r="E55" s="43" t="s">
-        <v>161</v>
       </c>
       <c r="F55" s="43">
         <v>3001234568</v>
       </c>
       <c r="G55" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="43" t="s">
         <v>162</v>
-      </c>
-      <c r="H55" s="43" t="s">
-        <v>163</v>
       </c>
       <c r="I55" s="45"/>
       <c r="J55" s="45"/>
@@ -12678,25 +12681,25 @@
         <v>2</v>
       </c>
       <c r="B56" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C56" s="43">
         <v>1098765434</v>
       </c>
       <c r="D56" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" s="43" t="s">
         <v>164</v>
-      </c>
-      <c r="E56" s="43" t="s">
-        <v>165</v>
       </c>
       <c r="F56" s="43">
         <v>3001234570</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H56" s="43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I56" s="45"/>
       <c r="J56" s="45"/>
@@ -12707,25 +12710,25 @@
         <v>3</v>
       </c>
       <c r="B57" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57" s="43">
         <v>1070971265</v>
       </c>
       <c r="D57" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="E57" s="43" t="s">
         <v>167</v>
-      </c>
-      <c r="E57" s="43" t="s">
-        <v>168</v>
       </c>
       <c r="F57" s="43">
         <v>3131234567</v>
       </c>
       <c r="G57" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="H57" s="43" t="s">
         <v>169</v>
-      </c>
-      <c r="H57" s="43" t="s">
-        <v>170</v>
       </c>
       <c r="I57" s="45"/>
       <c r="J57" s="45"/>
@@ -12736,25 +12739,25 @@
         <v>4</v>
       </c>
       <c r="B58" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="43">
         <v>1111111111</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E58" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F58" s="43">
         <v>3131234568</v>
       </c>
       <c r="G58" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I58" s="45"/>
       <c r="J58" s="45"/>
@@ -12765,25 +12768,25 @@
         <v>5</v>
       </c>
       <c r="B59" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C59" s="43">
         <v>55555555</v>
       </c>
       <c r="D59" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" s="43" t="s">
         <v>173</v>
-      </c>
-      <c r="E59" s="43" t="s">
-        <v>174</v>
       </c>
       <c r="F59" s="43">
         <v>5050505050</v>
       </c>
       <c r="G59" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="H59" s="43" t="s">
         <v>175</v>
-      </c>
-      <c r="H59" s="43" t="s">
-        <v>176</v>
       </c>
       <c r="I59" s="45"/>
       <c r="J59" s="45"/>
@@ -12818,38 +12821,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -12891,24 +12894,24 @@
         <v>17</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1">
       <c r="A6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>28</v>
@@ -12917,154 +12920,154 @@
         <v>17</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1">
       <c r="A7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1">
       <c r="A9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>65</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>66</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1">
       <c r="A10" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>67</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>68</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1">
       <c r="A11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>70</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>71</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.25" customHeight="1">
       <c r="A12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>28</v>
@@ -13073,24 +13076,24 @@
         <v>17</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1">
       <c r="A13" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>28</v>
@@ -13099,199 +13102,199 @@
         <v>17</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
       <c r="A14" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>79</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>80</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>82</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>83</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>85</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>86</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>88</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>89</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>91</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>92</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>94</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1">
       <c r="A20" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="25" t="s">
         <v>97</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>98</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1"/>
@@ -14301,38 +14304,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -14377,105 +14380,105 @@
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G6" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="60" t="s">
-        <v>179</v>
+      <c r="H6" s="46" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G7" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="60" t="s">
-        <v>179</v>
+      <c r="H7" s="46" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="46" t="s">
         <v>187</v>
-      </c>
-      <c r="F8" s="60" t="s">
-        <v>185</v>
-      </c>
-      <c r="G8" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="60" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="15"/>
@@ -14488,16 +14491,16 @@
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21"/>
@@ -15527,38 +15530,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -15609,7 +15612,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
@@ -15626,7 +15629,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>20</v>
@@ -15635,102 +15638,102 @@
         <v>21</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>52</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>55</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>20</v>
@@ -15739,7 +15742,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1"/>

--- a/Tabla de endpoints.xlsx
+++ b/Tabla de endpoints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyecto Peluquería\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E5B6B-F2CD-4A1A-98EE-13EFD74C9F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508896E9-754E-4E35-A3DA-FD28BFF93FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bitácora" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="193">
   <si>
     <t>v</t>
   </si>
@@ -121,9 +121,6 @@
     <t>/seguridad/crearcliente</t>
   </si>
   <si>
-    <t>Creado//PTE POR ´PRUEBAS</t>
-  </si>
-  <si>
     <t>vista/admin/RutasAdmin.js</t>
   </si>
   <si>
@@ -217,9 +214,6 @@
     <t>Cliente desactiva su cuenta</t>
   </si>
   <si>
-    <t>Creado//PTE POR PROBAR</t>
-  </si>
-  <si>
     <t>/usuario/desactivar/:idcliente</t>
   </si>
   <si>
@@ -599,6 +593,21 @@
   </si>
   <si>
     <t>Creado 18/10/2026. Función probada OK</t>
+  </si>
+  <si>
+    <t>/trabajador/horarios/:idhorario</t>
+  </si>
+  <si>
+    <t>RF - 26</t>
+  </si>
+  <si>
+    <t>Cliente crea cita</t>
+  </si>
+  <si>
+    <t>/citas</t>
+  </si>
+  <si>
+    <t>vista/clientes/RutasCitas.js</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1384,7 @@
         <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
@@ -1424,7 +1433,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>20</v>
@@ -1438,10 +1447,10 @@
     </row>
     <row r="8" spans="1:26" ht="15.5">
       <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>28</v>
@@ -1450,10 +1459,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>21</v>
@@ -1479,7 +1488,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>21</v>
@@ -1507,22 +1516,22 @@
     </row>
     <row r="10" spans="1:26" ht="15.5">
       <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>21</v>
@@ -1533,22 +1542,22 @@
     </row>
     <row r="11" spans="1:26" ht="15.5">
       <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>21</v>
@@ -1559,48 +1568,48 @@
     </row>
     <row r="12" spans="1:26" ht="15.5">
       <c r="A12" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="46" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.5">
       <c r="A13" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>185</v>
+        <v>36</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F13" s="46" t="s">
-        <v>184</v>
+        <v>177</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>21</v>
@@ -1611,45 +1620,49 @@
     </row>
     <row r="14" spans="1:26" ht="15.5">
       <c r="A14" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>186</v>
+        <v>33</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="G14" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.5">
       <c r="A15" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+        <v>47</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>182</v>
+      </c>
       <c r="G15" s="15" t="s">
         <v>21</v>
       </c>
@@ -1659,19 +1672,23 @@
     </row>
     <row r="16" spans="1:26" ht="15.5">
       <c r="A16" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+        <v>59</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="G16" s="21" t="s">
         <v>21</v>
       </c>
@@ -1681,22 +1698,22 @@
     </row>
     <row r="17" spans="1:26" ht="15.5">
       <c r="A17" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>21</v>
@@ -1707,22 +1724,22 @@
     </row>
     <row r="18" spans="1:26" ht="15.5">
       <c r="A18" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>21</v>
@@ -1733,22 +1750,22 @@
     </row>
     <row r="19" spans="1:26" ht="15.5">
       <c r="A19" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="21" t="s">
         <v>21</v>
@@ -1759,22 +1776,22 @@
     </row>
     <row r="20" spans="1:26" ht="15.5">
       <c r="A20" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>21</v>
@@ -1785,22 +1802,22 @@
     </row>
     <row r="21" spans="1:26" ht="14.25" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>50</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>51</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>21</v>
@@ -1829,22 +1846,22 @@
     </row>
     <row r="22" spans="1:26" ht="14.25" customHeight="1">
       <c r="A22" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>54</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G22" s="15" t="s">
         <v>21</v>
@@ -1873,10 +1890,10 @@
     </row>
     <row r="23" spans="1:26" ht="15.5">
       <c r="A23" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>28</v>
@@ -1885,10 +1902,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>21</v>
@@ -1899,10 +1916,10 @@
     </row>
     <row r="24" spans="1:26" ht="15.5">
       <c r="A24" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>28</v>
@@ -1911,10 +1928,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>21</v>
@@ -1925,22 +1942,22 @@
     </row>
     <row r="25" spans="1:26" ht="15.5">
       <c r="A25" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>21</v>
@@ -1951,22 +1968,22 @@
     </row>
     <row r="26" spans="1:26" ht="15.5">
       <c r="A26" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>21</v>
@@ -1977,22 +1994,22 @@
     </row>
     <row r="27" spans="1:26" ht="15.5">
       <c r="A27" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="15" t="s">
         <v>21</v>
@@ -2003,22 +2020,22 @@
     </row>
     <row r="28" spans="1:26" ht="15.5">
       <c r="A28" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>21</v>
@@ -2029,19 +2046,19 @@
     </row>
     <row r="29" spans="1:26" ht="15.5">
       <c r="A29" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>20</v>
@@ -2055,22 +2072,22 @@
     </row>
     <row r="30" spans="1:26" ht="15.5">
       <c r="A30" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" s="15" t="s">
         <v>21</v>
@@ -2081,22 +2098,22 @@
     </row>
     <row r="31" spans="1:26" ht="15.5">
       <c r="A31" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31" s="15" t="s">
         <v>21</v>
@@ -2107,22 +2124,22 @@
     </row>
     <row r="32" spans="1:26" ht="15.5">
       <c r="A32" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C32" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G32" s="21" t="s">
         <v>21</v>
@@ -2132,14 +2149,30 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.5">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="31"/>
+      <c r="A33" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="34" spans="1:8" ht="15.5">
       <c r="A34" s="30"/>
@@ -11859,7 +11892,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="56" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -11869,127 +11902,127 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="D2" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="E2" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>103</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" s="35">
         <v>5</v>
       </c>
       <c r="C3" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="F3" s="34" t="s">
         <v>108</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B4" s="35">
         <v>13</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="34" t="s">
         <v>108</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B5" s="35">
         <v>13</v>
       </c>
       <c r="C5" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="F5" s="34" t="s">
         <v>108</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" s="35">
         <v>5</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="F6" s="34" t="s">
         <v>108</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="34" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="35">
         <v>36</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="56" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="56"/>
       <c r="C10" s="56"/>
@@ -12001,28 +12034,28 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="D11" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="E11" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="F11" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="G11" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="H11" s="36" t="s">
         <v>124</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -12030,25 +12063,25 @@
         <v>1</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C12" s="37">
         <v>12345678</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F12" s="37">
         <v>3001234567</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -12056,25 +12089,25 @@
         <v>2</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" s="37">
         <v>25865254</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F13" s="37">
         <v>3131234569</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -12082,25 +12115,25 @@
         <v>3</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C14" s="37">
         <v>33333333</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F14" s="37">
         <v>3030303030</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -12108,25 +12141,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C15" s="37">
         <v>33333335</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F15" s="37">
         <v>3030303035</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -12134,30 +12167,30 @@
         <v>5</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C16" s="37">
         <v>33333355</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F16" s="37">
         <v>3030303035</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B19" s="56"/>
       <c r="C19" s="56"/>
@@ -12166,19 +12199,19 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="D20" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>150</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -12195,7 +12228,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -12212,7 +12245,7 @@
         <v>0.375</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -12229,7 +12262,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -12246,7 +12279,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -12263,7 +12296,7 @@
         <v>0.5</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -12280,7 +12313,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -12297,7 +12330,7 @@
         <v>0.625</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -12314,7 +12347,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -12331,7 +12364,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -12348,7 +12381,7 @@
         <v>0.75</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -12365,7 +12398,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -12382,7 +12415,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -12399,12 +12432,12 @@
         <v>0.875</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="56" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B36" s="56"/>
       <c r="C36" s="56"/>
@@ -12412,16 +12445,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="36" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -12435,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -12449,7 +12482,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -12463,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -12477,7 +12510,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -12491,7 +12524,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -12505,7 +12538,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -12519,7 +12552,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -12533,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -12547,7 +12580,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -12561,7 +12594,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -12575,7 +12608,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -12589,7 +12622,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -12603,12 +12636,12 @@
         <v>1</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="58" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B53" s="58"/>
       <c r="C53" s="58"/>
@@ -12620,28 +12653,28 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="44" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B54" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="E54" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="F54" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="E54" s="44" t="s">
+      <c r="G54" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="F54" s="44" t="s">
+      <c r="H54" s="44" t="s">
         <v>124</v>
-      </c>
-      <c r="G54" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="H54" s="44" t="s">
-        <v>126</v>
       </c>
       <c r="I54" s="45"/>
       <c r="J54" s="45"/>
@@ -12652,25 +12685,25 @@
         <v>1</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C55" s="43">
         <v>1098765433</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F55" s="43">
         <v>3001234568</v>
       </c>
       <c r="G55" s="43" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H55" s="43" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I55" s="45"/>
       <c r="J55" s="45"/>
@@ -12681,25 +12714,25 @@
         <v>2</v>
       </c>
       <c r="B56" s="43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C56" s="43">
         <v>1098765434</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F56" s="43">
         <v>3001234570</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H56" s="43" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I56" s="45"/>
       <c r="J56" s="45"/>
@@ -12710,25 +12743,25 @@
         <v>3</v>
       </c>
       <c r="B57" s="43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C57" s="43">
         <v>1070971265</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F57" s="43">
         <v>3131234567</v>
       </c>
       <c r="G57" s="43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H57" s="43" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I57" s="45"/>
       <c r="J57" s="45"/>
@@ -12739,25 +12772,25 @@
         <v>4</v>
       </c>
       <c r="B58" s="43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C58" s="43">
         <v>1111111111</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E58" s="43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F58" s="43">
         <v>3131234568</v>
       </c>
       <c r="G58" s="43" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I58" s="45"/>
       <c r="J58" s="45"/>
@@ -12768,25 +12801,25 @@
         <v>5</v>
       </c>
       <c r="B59" s="43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C59" s="43">
         <v>55555555</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E59" s="43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F59" s="43">
         <v>5050505050</v>
       </c>
       <c r="G59" s="43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H59" s="43" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I59" s="45"/>
       <c r="J59" s="45"/>
@@ -12897,21 +12930,21 @@
         <v>29</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1">
       <c r="A6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>28</v>
@@ -12920,154 +12953,154 @@
         <v>17</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1">
       <c r="A7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>41</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>42</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1">
       <c r="A9" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1">
       <c r="A10" s="24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1">
       <c r="A11" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.25" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>28</v>
@@ -13076,24 +13109,24 @@
         <v>17</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.25" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>28</v>
@@ -13102,199 +13135,199 @@
         <v>17</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25" customHeight="1">
       <c r="A20" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.25" customHeight="1"/>
@@ -14380,135 +14413,143 @@
         <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G6" s="46" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G7" s="46" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G8" s="46" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="15"/>
+        <v>47</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>182</v>
+      </c>
       <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="21"/>
+        <v>59</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="G10" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1"/>
@@ -15612,7 +15653,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
@@ -15629,7 +15670,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>20</v>
@@ -15638,102 +15679,102 @@
         <v>21</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>54</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>20</v>
@@ -15742,10 +15783,35 @@
         <v>21</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:8" ht="14.25" customHeight="1"/>
